--- a/Science.xlsx
+++ b/Science.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Graph" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Tech Cost" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Education Efficiency" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="State Sim" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Goods values" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="126">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -306,12 +307,108 @@
   <si>
     <t xml:space="preserve">Cash</t>
   </si>
+  <si>
+    <t xml:space="preserve">RGO Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price per boi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precious Goods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pearls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precious Metal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slave Trade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tropical Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sulphur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cattle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coffee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tobacco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opium</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
@@ -320,6 +417,7 @@
     <numFmt numFmtId="169" formatCode="0.00"/>
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="0.0%"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -425,7 +523,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -506,15 +604,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -523,6 +617,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -535,6 +637,23 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1334,11 +1453,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73043078"/>
-        <c:axId val="95449965"/>
+        <c:axId val="66178995"/>
+        <c:axId val="96156831"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="73043078"/>
+        <c:axId val="66178995"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1403,7 +1522,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95449965"/>
+        <c:crossAx val="96156831"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1411,7 +1530,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95449965"/>
+        <c:axId val="96156831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1485,7 +1604,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73043078"/>
+        <c:crossAx val="66178995"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2306,11 +2425,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="89476834"/>
-        <c:axId val="87847165"/>
+        <c:axId val="65538593"/>
+        <c:axId val="86356392"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="89476834"/>
+        <c:axId val="65538593"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2375,7 +2494,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87847165"/>
+        <c:crossAx val="86356392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2383,7 +2502,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87847165"/>
+        <c:axId val="86356392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2457,7 +2576,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89476834"/>
+        <c:crossAx val="65538593"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2519,9 +2638,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>223200</xdr:colOff>
+      <xdr:colOff>222840</xdr:colOff>
       <xdr:row>141</xdr:row>
-      <xdr:rowOff>24840</xdr:rowOff>
+      <xdr:rowOff>24480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2530,7 +2649,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="416520" y="19726200"/>
-        <a:ext cx="14987520" cy="5816160"/>
+        <a:ext cx="14987160" cy="5815800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2554,9 +2673,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>477360</xdr:colOff>
+      <xdr:colOff>477000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>69120</xdr:rowOff>
+      <xdr:rowOff>68760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2565,7 +2684,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9032040" y="0"/>
-        <a:ext cx="7868160" cy="4801320"/>
+        <a:ext cx="7867800" cy="4800960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3990,7 +4109,7 @@
       </c>
       <c r="F28" s="10" t="n">
         <f aca="false">(MIN(B28,0.02)*150)+(MIN(C28,0.04)*50)+(MIN(D28,1)*4)+(IF(E28="Great Power",1.5,IF(E28="Secondary Power",1.25,IF(E28="Westernized Nation",1,0))))</f>
-        <v>5.82802171428571</v>
+        <v>5.82802171428572</v>
       </c>
       <c r="G28" s="2" t="n">
         <f aca="false">MIN(G27+(4*2/90/100*12),1)</f>
@@ -4001,7 +4120,7 @@
       </c>
       <c r="I28" s="10" t="n">
         <f aca="false">F28*(1+H28+G28)</f>
-        <v>15.020754631619</v>
+        <v>15.0207546316191</v>
       </c>
       <c r="J28" s="7" t="n">
         <f aca="false">I28*365</f>
@@ -4049,7 +4168,7 @@
       </c>
       <c r="J29" s="7" t="n">
         <f aca="false">I29*365</f>
-        <v>5554.82009716571</v>
+        <v>5554.82009716572</v>
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="6" t="n">
@@ -4122,7 +4241,7 @@
       </c>
       <c r="F31" s="10" t="n">
         <f aca="false">(MIN(B31,0.02)*150)+(MIN(C31,0.04)*50)+(MIN(D31,1)*4)+(IF(E31="Great Power",1.5,IF(E31="Secondary Power",1.25,IF(E31="Westernized Nation",1,0))))</f>
-        <v>5.98893828571429</v>
+        <v>5.98893828571428</v>
       </c>
       <c r="G31" s="2" t="n">
         <f aca="false">MIN(G30+(4*2/90/100*12),1)</f>
@@ -4137,7 +4256,7 @@
       </c>
       <c r="J31" s="7" t="n">
         <f aca="false">I31*365</f>
-        <v>5703.90474956953</v>
+        <v>5703.90474956952</v>
       </c>
       <c r="K31" s="8"/>
       <c r="L31" s="6" t="n">
@@ -4256,7 +4375,7 @@
       </c>
       <c r="F34" s="10" t="n">
         <f aca="false">(MIN(B34,0.02)*150)+(MIN(C34,0.04)*50)+(MIN(D34,1)*4)+(IF(E34="Great Power",1.5,IF(E34="Secondary Power",1.25,IF(E34="Westernized Nation",1,0))))</f>
-        <v>6.16046971428571</v>
+        <v>6.16046971428572</v>
       </c>
       <c r="G34" s="2" t="n">
         <f aca="false">MIN(G33+(4*2/90/100*12),1)</f>
@@ -4344,7 +4463,7 @@
       </c>
       <c r="F36" s="10" t="n">
         <f aca="false">(MIN(B36,0.02)*150)+(MIN(C36,0.04)*50)+(MIN(D36,1)*4)+(IF(E36="Great Power",1.5,IF(E36="Secondary Power",1.25,IF(E36="Westernized Nation",1,0))))</f>
-        <v>6.28366971428571</v>
+        <v>6.28366971428572</v>
       </c>
       <c r="G36" s="2" t="n">
         <f aca="false">MIN(G35+(4*2/90/100*12),1)</f>
@@ -4388,7 +4507,7 @@
       </c>
       <c r="F37" s="10" t="n">
         <f aca="false">(MIN(B37,0.02)*150)+(MIN(C37,0.04)*50)+(MIN(D37,1)*4)+(IF(E37="Great Power",1.5,IF(E37="Secondary Power",1.25,IF(E37="Westernized Nation",1,0))))</f>
-        <v>6.34858171428571</v>
+        <v>6.34858171428572</v>
       </c>
       <c r="G37" s="2" t="n">
         <f aca="false">MIN(G36+(4*2/90/100*12),1)</f>
@@ -4432,7 +4551,7 @@
       </c>
       <c r="F38" s="10" t="n">
         <f aca="false">(MIN(B38,0.02)*150)+(MIN(C38,0.04)*50)+(MIN(D38,1)*4)+(IF(E38="Great Power",1.5,IF(E38="Secondary Power",1.25,IF(E38="Westernized Nation",1,0))))</f>
-        <v>6.41474171428571</v>
+        <v>6.41474171428572</v>
       </c>
       <c r="G38" s="2" t="n">
         <f aca="false">MIN(G37+(4*2/90/100*12),1)</f>
@@ -4491,7 +4610,7 @@
       </c>
       <c r="J39" s="7" t="n">
         <f aca="false">I39*365</f>
-        <v>7558.53228150857</v>
+        <v>7558.53228150858</v>
       </c>
       <c r="K39" s="8"/>
       <c r="L39" s="6" t="n">
@@ -4520,7 +4639,7 @@
       </c>
       <c r="F40" s="10" t="n">
         <f aca="false">(MIN(B40,0.02)*150)+(MIN(C40,0.04)*50)+(MIN(D40,1)*4)+(IF(E40="Great Power",1.5,IF(E40="Secondary Power",1.25,IF(E40="Westernized Nation",1,0))))</f>
-        <v>6.55080571428571</v>
+        <v>6.55080571428572</v>
       </c>
       <c r="G40" s="2" t="n">
         <f aca="false">MIN(G39+(4*2/90/100*12),1)</f>
@@ -4535,7 +4654,7 @@
       </c>
       <c r="J40" s="7" t="n">
         <f aca="false">I40*365</f>
-        <v>7664.09330940952</v>
+        <v>7664.09330940953</v>
       </c>
       <c r="K40" s="8"/>
       <c r="L40" s="6" t="n">
@@ -4608,7 +4727,7 @@
       </c>
       <c r="F42" s="10" t="n">
         <f aca="false">(MIN(B42,0.02)*150)+(MIN(C42,0.04)*50)+(MIN(D42,1)*4)+(IF(E42="Great Power",1.5,IF(E42="Secondary Power",1.25,IF(E42="Westernized Nation",1,0))))</f>
-        <v>6.69186171428571</v>
+        <v>6.69186171428572</v>
       </c>
       <c r="G42" s="2" t="n">
         <f aca="false">MIN(G41+(4*2/90/100*12),1)</f>
@@ -4878,7 +4997,7 @@
       </c>
       <c r="F48" s="10" t="n">
         <f aca="false">(MIN(B48,0.02)*150)+(MIN(C48,0.04)*50)+(MIN(D48,1)*4)+(IF(E48="Great Power",1.5,IF(E48="Secondary Power",1.25,IF(E48="Westernized Nation",1,0))))</f>
-        <v>7.15578171428571</v>
+        <v>7.15578171428572</v>
       </c>
       <c r="G48" s="2" t="n">
         <f aca="false">MIN(G47+(4*2/90/100*12),1)</f>
@@ -4922,7 +5041,7 @@
       </c>
       <c r="F49" s="10" t="n">
         <f aca="false">(MIN(B49,0.02)*150)+(MIN(C49,0.04)*50)+(MIN(D49,1)*4)+(IF(E49="Great Power",1.5,IF(E49="Secondary Power",1.25,IF(E49="Westernized Nation",1,0))))</f>
-        <v>7.23758971428571</v>
+        <v>7.23758971428572</v>
       </c>
       <c r="G49" s="2" t="n">
         <f aca="false">MIN(G48+(4*2/90/100*12),1)</f>
@@ -5188,7 +5307,7 @@
       </c>
       <c r="F55" s="10" t="n">
         <f aca="false">(MIN(B55,0.02)*150)+(MIN(C55,0.04)*50)+(MIN(D55,1)*4)+(IF(E55="Great Power",1.5,IF(E55="Secondary Power",1.25,IF(E55="Westernized Nation",1,0))))</f>
-        <v>7.75536571428571</v>
+        <v>7.75536571428572</v>
       </c>
       <c r="G55" s="2" t="n">
         <f aca="false">MIN(G54+(4*2/90/100*12),1)</f>
@@ -5232,7 +5351,7 @@
       </c>
       <c r="F56" s="10" t="n">
         <f aca="false">(MIN(B56,0.02)*150)+(MIN(C56,0.04)*50)+(MIN(D56,1)*4)+(IF(E56="Great Power",1.5,IF(E56="Secondary Power",1.25,IF(E56="Westernized Nation",1,0))))</f>
-        <v>7.85262971428571</v>
+        <v>7.85262971428572</v>
       </c>
       <c r="G56" s="2" t="n">
         <f aca="false">MIN(G55+(4*2/90/100*12),1)</f>
@@ -5542,7 +5661,7 @@
       </c>
       <c r="F63" s="10" t="n">
         <f aca="false">(MIN(B63,0.02)*150)+(MIN(C63,0.04)*50)+(MIN(D63,1)*4)+(IF(E63="Great Power",1.5,IF(E63="Secondary Power",1.25,IF(E63="Westernized Nation",1,0))))</f>
-        <v>8.57226171428571</v>
+        <v>8.57226171428572</v>
       </c>
       <c r="G63" s="2" t="n">
         <f aca="false">MIN(G62+(4*2/90/100*12),1)</f>
@@ -5586,7 +5705,7 @@
       </c>
       <c r="F64" s="10" t="n">
         <f aca="false">(MIN(B64,0.02)*150)+(MIN(C64,0.04)*50)+(MIN(D64,1)*4)+(IF(E64="Great Power",1.5,IF(E64="Secondary Power",1.25,IF(E64="Westernized Nation",1,0))))</f>
-        <v>8.67922171428571</v>
+        <v>8.67922171428572</v>
       </c>
       <c r="G64" s="2" t="n">
         <f aca="false">MIN(G63+(4*2/90/100*12),1)</f>
@@ -5630,7 +5749,7 @@
       </c>
       <c r="F65" s="10" t="n">
         <f aca="false">(MIN(B65,0.02)*150)+(MIN(C65,0.04)*50)+(MIN(D65,1)*4)+(IF(E65="Great Power",1.5,IF(E65="Secondary Power",1.25,IF(E65="Westernized Nation",1,0))))</f>
-        <v>8.78618171428571</v>
+        <v>8.78618171428572</v>
       </c>
       <c r="G65" s="2" t="n">
         <f aca="false">MIN(G64+(4*2/90/100*12),1)</f>
@@ -5718,7 +5837,7 @@
       </c>
       <c r="F67" s="10" t="n">
         <f aca="false">(MIN(B67,0.02)*150)+(MIN(C67,0.04)*50)+(MIN(D67,1)*4)+(IF(E67="Great Power",1.5,IF(E67="Secondary Power",1.25,IF(E67="Westernized Nation",1,0))))</f>
-        <v>9.00010171428571</v>
+        <v>9.00010171428572</v>
       </c>
       <c r="G67" s="2" t="n">
         <f aca="false">MIN(G66+(4*2/90/100*12),1)</f>
@@ -5808,7 +5927,7 @@
       </c>
       <c r="F69" s="10" t="n">
         <f aca="false">(MIN(B69,0.02)*150)+(MIN(C69,0.04)*50)+(MIN(D69,1)*4)+(IF(E69="Great Power",1.5,IF(E69="Secondary Power",1.25,IF(E69="Westernized Nation",1,0))))</f>
-        <v>9.21402171428571</v>
+        <v>9.21402171428572</v>
       </c>
       <c r="G69" s="2" t="n">
         <f aca="false">MIN(G68+(4*2/90/100*12),1)</f>
@@ -11767,7 +11886,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="20.42"/>
@@ -11976,7 +12095,7 @@
         <f aca="false">SUM(X3)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="22" t="n">
+      <c r="X3" s="20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12029,7 +12148,7 @@
         <f aca="false">VLOOKUP(G4,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F4&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="V4" s="23" t="n">
+      <c r="V4" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="W4" s="21" t="n">
@@ -12089,7 +12208,7 @@
         <f aca="false">VLOOKUP(G5,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F5&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="V5" s="23" t="n">
+      <c r="V5" s="22" t="n">
         <v>0.2</v>
       </c>
       <c r="W5" s="15" t="n">
@@ -12149,7 +12268,7 @@
         <f aca="false">VLOOKUP(G6,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F6&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="V6" s="23" t="n">
+      <c r="V6" s="22" t="n">
         <v>0.3</v>
       </c>
       <c r="W6" s="15" t="n">
@@ -12209,7 +12328,7 @@
         <f aca="false">VLOOKUP(G7,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F7&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="V7" s="23" t="n">
+      <c r="V7" s="22" t="n">
         <v>0.4</v>
       </c>
       <c r="W7" s="15" t="n">
@@ -12269,7 +12388,7 @@
         <f aca="false">VLOOKUP(G8,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F8&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="V8" s="23" t="n">
+      <c r="V8" s="22" t="n">
         <v>0.51</v>
       </c>
       <c r="W8" s="15" t="n">
@@ -12329,7 +12448,7 @@
         <f aca="false">VLOOKUP(G9,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F9&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="V9" s="23" t="n">
+      <c r="V9" s="22" t="n">
         <v>0.62</v>
       </c>
       <c r="W9" s="15" t="n">
@@ -12389,7 +12508,7 @@
         <f aca="false">VLOOKUP(G10,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F10&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="V10" s="23" t="n">
+      <c r="V10" s="22" t="n">
         <v>0.75</v>
       </c>
       <c r="W10" s="15" t="n">
@@ -12449,7 +12568,7 @@
         <f aca="false">VLOOKUP(G11,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F11&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="V11" s="23" t="n">
+      <c r="V11" s="22" t="n">
         <v>0.9</v>
       </c>
       <c r="W11" s="15" t="n">
@@ -12690,21 +12809,21 @@
       <c r="T15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="U15" s="22" t="n">
+      <c r="U15" s="20" t="n">
         <f aca="false">SUM(V15)</f>
         <v>0</v>
       </c>
-      <c r="V15" s="22" t="n">
+      <c r="V15" s="20" t="n">
         <v>0</v>
       </c>
       <c r="X15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="22" t="n">
+      <c r="Y15" s="20" t="n">
         <f aca="false">SUM(Z15)</f>
         <v>0</v>
       </c>
-      <c r="Z15" s="22" t="n">
+      <c r="Z15" s="20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12757,7 +12876,7 @@
         <f aca="false">VLOOKUP(G16,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F16&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="T16" s="23" t="n">
+      <c r="T16" s="22" t="n">
         <v>0.3</v>
       </c>
       <c r="U16" s="14" t="n">
@@ -12767,7 +12886,7 @@
       <c r="V16" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="X16" s="23" t="n">
+      <c r="X16" s="22" t="n">
         <v>0.4</v>
       </c>
       <c r="Y16" s="14" t="n">
@@ -12827,7 +12946,7 @@
         <f aca="false">VLOOKUP(G17,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F17&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="T17" s="23" t="n">
+      <c r="T17" s="22" t="n">
         <v>0.4</v>
       </c>
       <c r="U17" s="14" t="n">
@@ -12837,7 +12956,7 @@
       <c r="V17" s="9" t="n">
         <v>0.0025</v>
       </c>
-      <c r="X17" s="23" t="n">
+      <c r="X17" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="Y17" s="14" t="n">
@@ -12897,7 +13016,7 @@
         <f aca="false">VLOOKUP(G18,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F18&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="T18" s="23" t="n">
+      <c r="T18" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="U18" s="14" t="n">
@@ -12907,7 +13026,7 @@
       <c r="V18" s="9" t="n">
         <v>0.0025</v>
       </c>
-      <c r="X18" s="23" t="n">
+      <c r="X18" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="Y18" s="14" t="n">
@@ -12967,7 +13086,7 @@
         <f aca="false">VLOOKUP(G19,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F19&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="T19" s="23" t="n">
+      <c r="T19" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="U19" s="14" t="n">
@@ -12977,7 +13096,7 @@
       <c r="V19" s="9" t="n">
         <v>0.0025</v>
       </c>
-      <c r="X19" s="23" t="n">
+      <c r="X19" s="22" t="n">
         <v>0.7</v>
       </c>
       <c r="Y19" s="14" t="n">
@@ -13037,7 +13156,7 @@
         <f aca="false">VLOOKUP(G20,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F20&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="T20" s="23" t="n">
+      <c r="T20" s="22" t="n">
         <v>0.7</v>
       </c>
       <c r="U20" s="14" t="n">
@@ -13047,7 +13166,7 @@
       <c r="V20" s="9" t="n">
         <v>0.0025</v>
       </c>
-      <c r="X20" s="23" t="n">
+      <c r="X20" s="22" t="n">
         <v>0.8</v>
       </c>
       <c r="Y20" s="14" t="n">
@@ -13107,7 +13226,7 @@
         <f aca="false">VLOOKUP(G21,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F21&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="T21" s="23" t="n">
+      <c r="T21" s="22" t="n">
         <v>0.8</v>
       </c>
       <c r="U21" s="14" t="n">
@@ -13117,7 +13236,7 @@
       <c r="V21" s="9" t="n">
         <v>0.0025</v>
       </c>
-      <c r="X21" s="23" t="n">
+      <c r="X21" s="22" t="n">
         <v>0.9</v>
       </c>
       <c r="Y21" s="14" t="n">
@@ -13177,10 +13296,10 @@
         <f aca="false">VLOOKUP(G22,$X$15:$Y$22,2,1)+VLOOKUP($P$2,$X$26:$Y$37,2,1)*IF(F22&gt;0.04,0,1)</f>
         <v>0.02</v>
       </c>
-      <c r="T22" s="23"/>
+      <c r="T22" s="22"/>
       <c r="U22" s="15"/>
-      <c r="V22" s="23"/>
-      <c r="X22" s="23" t="n">
+      <c r="V22" s="22"/>
+      <c r="X22" s="22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" s="14" t="n">
@@ -13191,13 +13310,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-    </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
       <c r="T24" s="18" t="s">
         <v>91</v>
       </c>
@@ -13210,8 +13323,6 @@
       <c r="Z24" s="18"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
       <c r="T25" s="6" t="s">
         <v>93</v>
       </c>
@@ -13232,33 +13343,29 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
       <c r="T26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="22" t="n">
+      <c r="U26" s="20" t="n">
         <f aca="false">SUM(V26)</f>
         <v>0</v>
       </c>
-      <c r="V26" s="22" t="n">
+      <c r="V26" s="20" t="n">
         <v>0</v>
       </c>
       <c r="X26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="Y26" s="22" t="n">
+      <c r="Y26" s="20" t="n">
         <f aca="false">SUM(Z26)</f>
         <v>0</v>
       </c>
-      <c r="Z26" s="22" t="n">
+      <c r="Z26" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="T27" s="23" t="n">
+      <c r="T27" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="U27" s="14" t="n">
@@ -13268,7 +13375,7 @@
       <c r="V27" s="9" t="n">
         <v>0.02</v>
       </c>
-      <c r="X27" s="23" t="n">
+      <c r="X27" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="Y27" s="14" t="n">
@@ -13280,9 +13387,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="T28" s="23" t="n">
+      <c r="T28" s="22" t="n">
         <v>0.2</v>
       </c>
       <c r="U28" s="14" t="n">
@@ -13292,7 +13397,7 @@
       <c r="V28" s="9" t="n">
         <v>0.02</v>
       </c>
-      <c r="X28" s="23" t="n">
+      <c r="X28" s="22" t="n">
         <v>0.2</v>
       </c>
       <c r="Y28" s="14" t="n">
@@ -13304,9 +13409,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="T29" s="23" t="n">
+      <c r="T29" s="22" t="n">
         <v>0.3</v>
       </c>
       <c r="U29" s="14" t="n">
@@ -13316,7 +13419,7 @@
       <c r="V29" s="9" t="n">
         <v>0.02</v>
       </c>
-      <c r="X29" s="23" t="n">
+      <c r="X29" s="22" t="n">
         <v>0.3</v>
       </c>
       <c r="Y29" s="14" t="n">
@@ -13328,9 +13431,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="T30" s="23" t="n">
+      <c r="T30" s="22" t="n">
         <v>0.4</v>
       </c>
       <c r="U30" s="14" t="n">
@@ -13340,7 +13441,7 @@
       <c r="V30" s="9" t="n">
         <v>0.022</v>
       </c>
-      <c r="X30" s="23" t="n">
+      <c r="X30" s="22" t="n">
         <v>0.4</v>
       </c>
       <c r="Y30" s="14" t="n">
@@ -13352,9 +13453,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="T31" s="23" t="n">
+      <c r="T31" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="U31" s="14" t="n">
@@ -13364,7 +13463,7 @@
       <c r="V31" s="9" t="n">
         <v>0.023</v>
       </c>
-      <c r="X31" s="23" t="n">
+      <c r="X31" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="Y31" s="14" t="n">
@@ -13376,9 +13475,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="T32" s="23" t="n">
+      <c r="T32" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="U32" s="14" t="n">
@@ -13388,7 +13485,7 @@
       <c r="V32" s="9" t="n">
         <v>0.025</v>
       </c>
-      <c r="X32" s="23" t="n">
+      <c r="X32" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="Y32" s="14" t="n">
@@ -13400,9 +13497,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="T33" s="23" t="n">
+      <c r="T33" s="22" t="n">
         <v>0.75</v>
       </c>
       <c r="U33" s="14" t="n">
@@ -13412,7 +13507,7 @@
       <c r="V33" s="9" t="n">
         <v>0.07</v>
       </c>
-      <c r="X33" s="23" t="n">
+      <c r="X33" s="22" t="n">
         <v>0.7</v>
       </c>
       <c r="Y33" s="14" t="n">
@@ -13424,9 +13519,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="T34" s="23" t="n">
+      <c r="T34" s="22" t="n">
         <v>0.8</v>
       </c>
       <c r="U34" s="14" t="n">
@@ -13436,7 +13529,7 @@
       <c r="V34" s="9" t="n">
         <v>0.02</v>
       </c>
-      <c r="X34" s="23" t="n">
+      <c r="X34" s="22" t="n">
         <v>0.75</v>
       </c>
       <c r="Y34" s="14" t="n">
@@ -13448,9 +13541,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="T35" s="23" t="n">
+      <c r="T35" s="22" t="n">
         <v>0.9</v>
       </c>
       <c r="U35" s="14" t="n">
@@ -13460,7 +13551,7 @@
       <c r="V35" s="9" t="n">
         <v>0.02</v>
       </c>
-      <c r="X35" s="23" t="n">
+      <c r="X35" s="22" t="n">
         <v>0.8</v>
       </c>
       <c r="Y35" s="14" t="n">
@@ -13472,9 +13563,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="T36" s="23" t="n">
+      <c r="T36" s="22" t="n">
         <v>1</v>
       </c>
       <c r="U36" s="14" t="n">
@@ -13484,7 +13573,7 @@
       <c r="V36" s="9" t="n">
         <v>0.02</v>
       </c>
-      <c r="X36" s="23" t="n">
+      <c r="X36" s="22" t="n">
         <v>0.9</v>
       </c>
       <c r="Y36" s="14" t="n">
@@ -13496,9 +13585,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="X37" s="23" t="n">
+      <c r="X37" s="22" t="n">
         <v>1</v>
       </c>
       <c r="Y37" s="14" t="n">
@@ -13531,4 +13618,490 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultColWidth="13.4765625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="23" width="17.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="23" width="7.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="23" width="6.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="23" width="14.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="23" width="13.48"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="23" t="n">
+        <f aca="false">B2*C2*3</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" s="23" t="n">
+        <f aca="false">B3*C3*3</f>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" s="23" t="n">
+        <f aca="false">B4*C4*3</f>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <f aca="false">B5*C5*3</f>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <f aca="false">B6*C6*3</f>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <f aca="false">B7*C7*3</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <f aca="false">B8*C8*3</f>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <f aca="false">B9*C9*3</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <f aca="false">B10*C10</f>
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <f aca="false">B11*C11</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <f aca="false">B12*C12</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <f aca="false">B13*C13</f>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <f aca="false">B14*C14</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <f aca="false">B15*C15</f>
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <f aca="false">B16*C16</f>
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <f aca="false">B17*C17</f>
+        <v>4.86</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <f aca="false">B18*C18</f>
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C19" s="23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D19" s="23" t="n">
+        <f aca="false">B19*C19</f>
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <f aca="false">B20*C20</f>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <f aca="false">B21*C21</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <f aca="false">B22*C22</f>
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <f aca="false">B23*C23</f>
+        <v>3.2</v>
+      </c>
+      <c r="H23" s="0"/>
+      <c r="I23" s="0"/>
+      <c r="J23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D24" s="23" t="n">
+        <f aca="false">B24*C24</f>
+        <v>3.15</v>
+      </c>
+      <c r="H24" s="0"/>
+      <c r="I24" s="0"/>
+      <c r="J24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C25" s="23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D25" s="23" t="n">
+        <f aca="false">B25*C25</f>
+        <v>3.15</v>
+      </c>
+      <c r="H25" s="0"/>
+      <c r="I25" s="0"/>
+      <c r="J25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D26" s="23" t="n">
+        <f aca="false">B26*C26</f>
+        <v>2.75</v>
+      </c>
+      <c r="H26" s="0"/>
+      <c r="I26" s="0"/>
+      <c r="J26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C27" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" s="23" t="n">
+        <f aca="false">B27*C27</f>
+        <v>2.64</v>
+      </c>
+      <c r="H27" s="0"/>
+      <c r="I27" s="0"/>
+      <c r="J27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" s="23" t="n">
+        <f aca="false">B28*C28</f>
+        <v>2.5</v>
+      </c>
+      <c r="H28" s="0"/>
+      <c r="I28" s="0"/>
+      <c r="J28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <f aca="false">B29*C29</f>
+        <v>2.24</v>
+      </c>
+      <c r="H29" s="0"/>
+      <c r="I29" s="0"/>
+      <c r="J29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="0"/>
+      <c r="I30" s="0"/>
+      <c r="J30" s="0"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normalny"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normalny"&amp;12&amp;KffffffStrona &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>